--- a/debug/excel_overviews/gpt-4.1_vs_Qwen2-7B-Instruct/Llama-3.1-8B-Instruct/metrics_default_vs_simple.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Qwen2-7B-Instruct/Llama-3.1-8B-Instruct/metrics_default_vs_simple.xlsx
@@ -420,25 +420,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.4</v>
+        <v>0.6382978723404256</v>
       </c>
       <c r="B2">
-        <v>0.3333333333333333</v>
+        <v>0.02777777777777778</v>
       </c>
       <c r="C2">
-        <v>0.6428571428571429</v>
+        <v>0.3829787234042553</v>
       </c>
       <c r="D2">
-        <v>0.625</v>
+        <v>0.7310924369747899</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>47</v>
       </c>
       <c r="F2">
-        <v>3</v>
+        <v>72</v>
       </c>
       <c r="G2">
-        <v>6</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>

--- a/debug/excel_overviews/gpt-4.1_vs_Qwen2-7B-Instruct/Llama-3.1-8B-Instruct/metrics_default_vs_simple.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Qwen2-7B-Instruct/Llama-3.1-8B-Instruct/metrics_default_vs_simple.xlsx
@@ -420,25 +420,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.6382978723404256</v>
+        <v>0.6122448979591837</v>
       </c>
       <c r="B2">
-        <v>0.02777777777777778</v>
+        <v>0.05797101449275362</v>
       </c>
       <c r="C2">
-        <v>0.3829787234042553</v>
+        <v>0.3777777777777778</v>
       </c>
       <c r="D2">
-        <v>0.7310924369747899</v>
+        <v>0.711864406779661</v>
       </c>
       <c r="E2">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F2">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G2">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
